--- a/latest.xlsx
+++ b/latest.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\vrfs01.ss.local\Users\r160610\デスクトップ\アプリ作成\RENKEI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F7EBEC1-C5F1-4CF6-B439-CBFB42EDA6BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02937825-239C-42B7-8C2E-94068D8B8798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57690" windowHeight="14475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57750" windowHeight="14475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="latest" sheetId="1" r:id="rId1"/>
@@ -924,8 +924,12 @@
       <c r="C29" s="3">
         <v>7</v>
       </c>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
+      <c r="D29" s="3">
+        <v>22</v>
+      </c>
+      <c r="E29" s="3">
+        <v>1086</v>
+      </c>
     </row>
     <row r="30" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A30" s="2" t="s">
